--- a/wwwroot/template/ExportSampleExcel.xlsx
+++ b/wwwroot/template/ExportSampleExcel.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -457,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -512,9 +512,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1026,18 +1023,18 @@
       <c r="AO3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1259,79 +1256,79 @@
       <c r="AO8" s="1"/>
     </row>
     <row r="9" spans="1:43" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="23" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="23"/>
-      <c r="AG9" s="23"/>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="23"/>
-      <c r="AJ9" s="23"/>
-      <c r="AK9" s="23"/>
-      <c r="AL9" s="23"/>
-      <c r="AM9" s="23"/>
-      <c r="AN9" s="23"/>
-      <c r="AO9" s="23"/>
-      <c r="AP9" s="23"/>
-      <c r="AQ9" s="23"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="22"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="22"/>
+      <c r="AM9" s="22"/>
+      <c r="AN9" s="22"/>
+      <c r="AO9" s="22"/>
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="26"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="25"/>
       <c r="T11" s="14"/>
       <c r="U11" s="14"/>
       <c r="V11" s="15"/>
@@ -1424,51 +1421,51 @@
       <c r="AO12"/>
     </row>
     <row r="13" spans="1:43" s="6" customFormat="1" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="30" t="s">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="30"/>
-      <c r="AC13" s="30"/>
-      <c r="AD13" s="30"/>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="30"/>
-      <c r="AJ13" s="30"/>
-      <c r="AK13" s="30"/>
-      <c r="AL13" s="30"/>
-      <c r="AM13" s="30"/>
-      <c r="AN13" s="30"/>
-      <c r="AO13" s="30"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="29"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="29"/>
+      <c r="AL13" s="29"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="29"/>
     </row>
     <row r="14" spans="1:43" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
@@ -1534,7 +1531,7 @@
       <c r="U14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="V14" s="20" t="s">
+      <c r="V14" s="7" t="s">
         <v>49</v>
       </c>
       <c r="W14" s="9" t="s">
